--- a/output/master_register.xlsx
+++ b/output/master_register.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,102 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-ANA-SVL-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DDD52MN3XCB6YBD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-ANV-SVL-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JBOA6DY5HEVS5VAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-ANV-SVL-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VI5NAR2U7UJUQ75P</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-ANV-SVL-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G7KKZQVFT5RSEXLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-KHA-LMX-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CCX2QDL6IJJ3SCRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-20K-SVL-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EVNPVZZ4PINRHY3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-ANV-SVL-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B5J6XXJHV3RQQQWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WC-2C-40A-000X-640E-8BI-SWA-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5LEPA4HRFWDM47M4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
